--- a/Result/R-L.xlsx
+++ b/Result/R-L.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajap\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajap\Downloads\Studio_1_DoF\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45FEE785-09DE-4AE7-BEA0-1ABFBBCC6E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EEA794-2DA2-4E90-9054-A155F43B2478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D946C786-B9E6-4FBE-A221-C1E65B1EF33B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>6V</t>
   </si>
@@ -69,6 +69,18 @@
   </si>
   <si>
     <t>12V</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>rad/s</t>
+  </si>
+  <si>
+    <t>Ke</t>
+  </si>
+  <si>
+    <t>Iavg</t>
   </si>
 </sst>
 </file>
@@ -283,8 +295,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -294,36 +326,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,331 +671,381 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
-      <c r="H1" s="10" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="21"/>
+      <c r="H1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="19"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="F2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
         <v>96</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>12</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>9.6</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="2">
         <v>10</v>
       </c>
-      <c r="H3" s="4">
+      <c r="F3">
+        <f>B3/$D$3</f>
+        <v>0.625</v>
+      </c>
+      <c r="G3">
+        <v>2.3788659999999999</v>
+      </c>
+      <c r="H3" s="1">
         <f>$D$3*(($C$3/B3)-1)</f>
         <v>9.6</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="11">
         <f>$D$3*((A3*10^-6)*($C$3/B3))</f>
         <v>1.8431999999999999E-3</v>
       </c>
-      <c r="J3" s="22"/>
+      <c r="J3" s="14"/>
+      <c r="K3">
+        <f>(C3-(F8*L11))/G3</f>
+        <v>2.6198565389105104</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="1">
         <v>98</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>6.2</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="H4" s="4">
-        <f t="shared" ref="H4:H7" si="0">$D$3*(($C$3/B4)-1)</f>
+      <c r="E4" s="2"/>
+      <c r="F4">
+        <f t="shared" ref="F4:F7" si="0">B4/$D$3</f>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" ref="H4:H7" si="1">$D$3*(($C$3/B4)-1)</f>
         <v>8.9806451612903206</v>
       </c>
-      <c r="I4" s="17">
-        <f t="shared" ref="I4:I7" si="1">$D$3*((A4*10^-6)*($C$3/B4))</f>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I7" si="2">$D$3*((A4*10^-6)*($C$3/B4))</f>
         <v>1.8209032258064512E-3</v>
       </c>
-      <c r="J4" s="22"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="1">
         <v>96</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>6</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="H5" s="4">
+      <c r="E5" s="2"/>
+      <c r="F5">
         <f t="shared" si="0"/>
+        <v>0.625</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8431999999999999E-3</v>
+      </c>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>98</v>
+      </c>
+      <c r="B6">
+        <v>6.2</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H6" s="1">
         <f t="shared" si="1"/>
-        <v>1.8431999999999999E-3</v>
-      </c>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>98</v>
-      </c>
-      <c r="B6" s="5">
+        <v>8.9806451612903206</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8209032258064512E-3</v>
+      </c>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>96</v>
+      </c>
+      <c r="B7" s="4">
         <v>6.2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="H6" s="4">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7">
         <f t="shared" si="0"/>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
         <v>8.9806451612903206</v>
       </c>
-      <c r="I6" s="17">
-        <f t="shared" si="1"/>
-        <v>1.8209032258064512E-3</v>
-      </c>
-      <c r="J6" s="22"/>
-    </row>
-    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
-        <v>96</v>
-      </c>
-      <c r="B7" s="8">
-        <v>6.2</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="H7" s="7">
-        <f t="shared" si="0"/>
-        <v>8.9806451612903206</v>
-      </c>
-      <c r="I7" s="18">
-        <f t="shared" si="1"/>
+      <c r="I7" s="12">
+        <f t="shared" si="2"/>
         <v>1.7837419354838709E-3</v>
       </c>
-      <c r="J7" s="22"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H8" s="20">
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <f>AVERAGE(F3:F7)</f>
+        <v>0.63750000000000007</v>
+      </c>
+      <c r="H8" s="1">
         <f>AVERAGE(H3:H7)</f>
         <v>9.2283870967741919</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="11">
         <f>AVERAGE(I3:I7)</f>
         <v>1.8223896774193545E-3</v>
       </c>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K9" s="5"/>
-    </row>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="H10" s="10" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="H10" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="19"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="F11" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="16">
         <f>AVERAGE(H8,H17)</f>
         <v>9.0473919289538962</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
+      <c r="A12" s="1">
         <v>90</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>3.12</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>6</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>9.6</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="2">
         <v>4.8</v>
       </c>
-      <c r="H12" s="4">
+      <c r="F12">
+        <f>B12/$D$12</f>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="H12" s="1">
         <f>$D$12*(($C$12/B12)-1)</f>
         <v>8.8615384615384603</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="11">
         <f>$D$12*((A12*10^-6)*($C$12/B12))</f>
         <v>1.661538461538461E-3</v>
       </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="26" t="s">
+      <c r="J12" s="14"/>
+      <c r="K12" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="18">
         <f>AVERAGE(I8,I17)</f>
         <v>1.7419057698837663E-3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="A13" s="1">
         <v>86</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>3.12</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="H13" s="4">
-        <f t="shared" ref="H13:H16" si="2">$D$12*(($C$12/B13)-1)</f>
+      <c r="E13" s="2"/>
+      <c r="F13">
+        <f t="shared" ref="F13:F16" si="3">B13/$D$12</f>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" ref="H13:H16" si="4">$D$12*(($C$12/B13)-1)</f>
         <v>8.8615384615384603</v>
       </c>
-      <c r="I13" s="17">
-        <f t="shared" ref="I13:I16" si="3">$D$12*((A13*10^-6)*($C$12/B13))</f>
+      <c r="I13" s="11">
+        <f t="shared" ref="I13:I16" si="5">$D$12*((A13*10^-6)*($C$12/B13))</f>
         <v>1.5876923076923071E-3</v>
       </c>
-      <c r="J13" s="22"/>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="1">
         <v>88</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>3.12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-      <c r="H14" s="4">
-        <f t="shared" si="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14">
+        <f t="shared" si="3"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="4"/>
         <v>8.8615384615384603</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="11">
+        <f t="shared" si="5"/>
+        <v>1.6246153846153843E-3</v>
+      </c>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>96</v>
+      </c>
+      <c r="B15">
+        <v>3.2</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15">
         <f t="shared" si="3"/>
-        <v>1.6246153846153843E-3</v>
-      </c>
-      <c r="J14" s="22"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>96</v>
-      </c>
-      <c r="B15" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="H15" s="4">
-        <f t="shared" si="2"/>
+        <v>0.33333333333333337</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="4"/>
         <v>8.4</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="11">
+        <f t="shared" si="5"/>
+        <v>1.7280000000000002E-3</v>
+      </c>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>90</v>
+      </c>
+      <c r="B16" s="4">
+        <v>3.04</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16">
         <f t="shared" si="3"/>
-        <v>1.7280000000000002E-3</v>
-      </c>
-      <c r="J15" s="22"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
-        <v>90</v>
-      </c>
-      <c r="B16" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9"/>
-      <c r="H16" s="7">
-        <f t="shared" si="2"/>
+        <v>0.31666666666666671</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="4"/>
         <v>9.3473684210526304</v>
       </c>
-      <c r="I16" s="18">
-        <f t="shared" si="3"/>
+      <c r="I16" s="12">
+        <f t="shared" si="5"/>
         <v>1.7052631578947366E-3</v>
       </c>
-      <c r="J16" s="22"/>
+      <c r="J16" s="14"/>
     </row>
     <row r="17" spans="8:10" x14ac:dyDescent="0.3">
-      <c r="H17" s="20">
+      <c r="H17" s="1">
         <f>AVERAGE(H12:H16)</f>
         <v>8.8663967611336023</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="11">
         <f>AVERAGE(I12:I16)</f>
         <v>1.6614218623481781E-3</v>
       </c>
-      <c r="J17" s="23"/>
+      <c r="J17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
